--- a/outputs/geo_spatial_stats.xlsx
+++ b/outputs/geo_spatial_stats.xlsx
@@ -651,7 +651,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>761.6208923809667</v>
+        <v>760.7249254466265</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -662,7 +662,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>366.3319961252419</v>
+        <v>367.2606063018525</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -673,7 +673,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>224.7380761411263</v>
+        <v>224.353388997563</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -684,7 +684,7 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>129.4391267822657</v>
+        <v>129.5997411597099</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -695,7 +695,7 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>396.9867302289278</v>
+        <v>397.3376949619366</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>268.3271256090866</v>
+        <v>268.3843488563369</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -717,7 +717,7 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>1693.713085159807</v>
+        <v>1693.572377630412</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -728,7 +728,7 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>1129.496421154182</v>
+        <v>1105.442682633964</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -739,7 +739,7 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>1782.370173642894</v>
+        <v>1783.747283001748</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -750,7 +750,7 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>115.6159125568454</v>
+        <v>115.9169175023088</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -761,7 +761,7 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>657.6704961572924</v>
+        <v>657.7101841964064</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -772,7 +772,7 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>935.8299155109588</v>
+        <v>935.9543755315033</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -783,7 +783,7 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>1538.67095069796</v>
+        <v>1538.9896816228</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -794,7 +794,7 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>105.8284781199683</v>
+        <v>106.0508645065856</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -805,7 +805,7 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>357.9410575011049</v>
+        <v>358.2471900781778</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -816,7 +816,7 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>1212.045814592163</v>
+        <v>1212.290285512076</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -827,7 +827,7 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>264.4868870666639</v>
+        <v>264.7755914388144</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
@@ -838,7 +838,7 @@
         <v>21</v>
       </c>
       <c r="B19">
-        <v>315.147738113812</v>
+        <v>315.742931686186</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
@@ -849,7 +849,7 @@
         <v>22</v>
       </c>
       <c r="B20">
-        <v>581.861334118146</v>
+        <v>582.0425431565758</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
@@ -860,7 +860,7 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>361.3806737189068</v>
+        <v>360.9791588770014</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -871,7 +871,7 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>293.8994321615687</v>
+        <v>293.9001375395331</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
@@ -882,7 +882,7 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>277.3645721203505</v>
+        <v>277.6387050865425</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -893,7 +893,7 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>70.97469521067249</v>
+        <v>70.82400226177489</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -904,7 +904,7 @@
         <v>27</v>
       </c>
       <c r="B25">
-        <v>749.4718399140905</v>
+        <v>749.675842484855</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -915,7 +915,7 @@
         <v>28</v>
       </c>
       <c r="B26">
-        <v>977.7404030340294</v>
+        <v>977.9020420680006</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
@@ -926,7 +926,7 @@
         <v>29</v>
       </c>
       <c r="B27">
-        <v>103.4086049849635</v>
+        <v>103.6178445452273</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
@@ -937,7 +937,7 @@
         <v>30</v>
       </c>
       <c r="B28">
-        <v>548.0485353772867</v>
+        <v>545.3414059931569</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -948,7 +948,7 @@
         <v>3</v>
       </c>
       <c r="B29">
-        <v>67.25001813808062</v>
+        <v>18.1468302912281</v>
       </c>
       <c r="C29" t="s">
         <v>31</v>
@@ -959,7 +959,7 @@
         <v>5</v>
       </c>
       <c r="B30">
-        <v>135.6988243144004</v>
+        <v>113.6830247105905</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
@@ -970,7 +970,7 @@
         <v>6</v>
       </c>
       <c r="B31">
-        <v>52.32549498306765</v>
+        <v>14.88354558446479</v>
       </c>
       <c r="C31" t="s">
         <v>31</v>
@@ -981,7 +981,7 @@
         <v>7</v>
       </c>
       <c r="B32">
-        <v>10.89184498677155</v>
+        <v>4.173783617492655</v>
       </c>
       <c r="C32" t="s">
         <v>31</v>
@@ -992,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="B33">
-        <v>153.3787802251116</v>
+        <v>123.0875237166268</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -1003,7 +1003,7 @@
         <v>9</v>
       </c>
       <c r="B34">
-        <v>324.9365537246113</v>
+        <v>214.9518090430962</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
@@ -1014,7 +1014,7 @@
         <v>10</v>
       </c>
       <c r="B35">
-        <v>27.21449156777539</v>
+        <v>12.59228926670447</v>
       </c>
       <c r="C35" t="s">
         <v>31</v>
@@ -1025,7 +1025,7 @@
         <v>11</v>
       </c>
       <c r="B36">
-        <v>170.6191924335079</v>
+        <v>74.47665136494027</v>
       </c>
       <c r="C36" t="s">
         <v>31</v>
@@ -1036,7 +1036,7 @@
         <v>12</v>
       </c>
       <c r="B37">
-        <v>62.71252183793935</v>
+        <v>47.19195464795877</v>
       </c>
       <c r="C37" t="s">
         <v>31</v>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
       <c r="B38">
-        <v>51.40529400277442</v>
+        <v>36.89137490555263</v>
       </c>
       <c r="C38" t="s">
         <v>31</v>
@@ -1058,7 +1058,7 @@
         <v>14</v>
       </c>
       <c r="B39">
-        <v>294.4720208791497</v>
+        <v>227.7820589871915</v>
       </c>
       <c r="C39" t="s">
         <v>31</v>
@@ -1069,7 +1069,7 @@
         <v>15</v>
       </c>
       <c r="B40">
-        <v>498.3658184716266</v>
+        <v>114.3111642140532</v>
       </c>
       <c r="C40" t="s">
         <v>31</v>
@@ -1080,7 +1080,7 @@
         <v>16</v>
       </c>
       <c r="B41">
-        <v>196.5821881713077</v>
+        <v>155.9401117997334</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
@@ -1091,7 +1091,7 @@
         <v>17</v>
       </c>
       <c r="B42">
-        <v>57.78838556090096</v>
+        <v>28.80723400106806</v>
       </c>
       <c r="C42" t="s">
         <v>31</v>
@@ -1102,7 +1102,7 @@
         <v>18</v>
       </c>
       <c r="B43">
-        <v>177.5011666846259</v>
+        <v>131.1837535976336</v>
       </c>
       <c r="C43" t="s">
         <v>31</v>
@@ -1113,7 +1113,7 @@
         <v>19</v>
       </c>
       <c r="B44">
-        <v>20.45328340547615</v>
+        <v>9.357281171826848</v>
       </c>
       <c r="C44" t="s">
         <v>31</v>
@@ -1124,7 +1124,7 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>194.4231476852588</v>
+        <v>99.65401283102314</v>
       </c>
       <c r="C45" t="s">
         <v>31</v>
@@ -1135,7 +1135,7 @@
         <v>21</v>
       </c>
       <c r="B46">
-        <v>94.90797018994768</v>
+        <v>75.87266356128049</v>
       </c>
       <c r="C46" t="s">
         <v>31</v>
@@ -1146,7 +1146,7 @@
         <v>22</v>
       </c>
       <c r="B47">
-        <v>264.1619171688866</v>
+        <v>202.5028770043829</v>
       </c>
       <c r="C47" t="s">
         <v>31</v>
@@ -1157,7 +1157,7 @@
         <v>23</v>
       </c>
       <c r="B48">
-        <v>5.639064915764338</v>
+        <v>1.690204324382488</v>
       </c>
       <c r="C48" t="s">
         <v>31</v>
@@ -1168,7 +1168,7 @@
         <v>24</v>
       </c>
       <c r="B49">
-        <v>105.898746505972</v>
+        <v>88.07331630847186</v>
       </c>
       <c r="C49" t="s">
         <v>31</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="B50">
-        <v>119.8505813666094</v>
+        <v>40.26942982855918</v>
       </c>
       <c r="C50" t="s">
         <v>31</v>
@@ -1190,7 +1190,7 @@
         <v>26</v>
       </c>
       <c r="B51">
-        <v>149.2739937838233</v>
+        <v>61.76264161675046</v>
       </c>
       <c r="C51" t="s">
         <v>31</v>
@@ -1201,7 +1201,7 @@
         <v>27</v>
       </c>
       <c r="B52">
-        <v>12.4864596753001</v>
+        <v>2.519589890469162</v>
       </c>
       <c r="C52" t="s">
         <v>31</v>
@@ -1212,7 +1212,7 @@
         <v>28</v>
       </c>
       <c r="B53">
-        <v>26.25349444801241</v>
+        <v>9.69468052802868</v>
       </c>
       <c r="C53" t="s">
         <v>31</v>
@@ -1223,7 +1223,7 @@
         <v>29</v>
       </c>
       <c r="B54">
-        <v>167.0590109613497</v>
+        <v>93.37583632616321</v>
       </c>
       <c r="C54" t="s">
         <v>31</v>
@@ -1234,7 +1234,7 @@
         <v>30</v>
       </c>
       <c r="B55">
-        <v>241.2797722684294</v>
+        <v>85.64141124851885</v>
       </c>
       <c r="C55" t="s">
         <v>31</v>
@@ -1245,7 +1245,7 @@
         <v>3</v>
       </c>
       <c r="B56">
-        <v>72.13933769774226</v>
+        <v>10.65360682863999</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -1256,7 +1256,7 @@
         <v>5</v>
       </c>
       <c r="B57">
-        <v>37.11232094043599</v>
+        <v>24.91581898666</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -1267,7 +1267,7 @@
         <v>6</v>
       </c>
       <c r="B58">
-        <v>28.90000634733787</v>
+        <v>9.990325118339383</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -1278,7 +1278,7 @@
         <v>7</v>
       </c>
       <c r="B59">
-        <v>19.81032332703572</v>
+        <v>13.52957110361621</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -1289,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="B60">
-        <v>53.95343031697146</v>
+        <v>41.34335787242581</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -1300,7 +1300,7 @@
         <v>9</v>
       </c>
       <c r="B61">
-        <v>26.80010861770792</v>
+        <v>7.645624680572847</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
       <c r="B62">
-        <v>15.91224391933893</v>
+        <v>2.618608506616466</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -1322,7 +1322,7 @@
         <v>11</v>
       </c>
       <c r="B63">
-        <v>67.56294097297004</v>
+        <v>12.99472341907263</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -1333,7 +1333,7 @@
         <v>12</v>
       </c>
       <c r="B64">
-        <v>31.53903856718597</v>
+        <v>20.79026595101068</v>
       </c>
       <c r="C64" t="s">
         <v>32</v>
@@ -1344,7 +1344,7 @@
         <v>13</v>
       </c>
       <c r="B65">
-        <v>19.45962174161331</v>
+        <v>9.261991768428196</v>
       </c>
       <c r="C65" t="s">
         <v>32</v>
@@ -1355,7 +1355,7 @@
         <v>14</v>
       </c>
       <c r="B66">
-        <v>98.44700785630522</v>
+        <v>72.69112413964704</v>
       </c>
       <c r="C66" t="s">
         <v>32</v>
@@ -1366,7 +1366,7 @@
         <v>15</v>
       </c>
       <c r="B67">
-        <v>51.25499690888518</v>
+        <v>9.403169138378297</v>
       </c>
       <c r="C67" t="s">
         <v>32</v>
@@ -1377,7 +1377,7 @@
         <v>16</v>
       </c>
       <c r="B68">
-        <v>13.80639958278007</v>
+        <v>6.939301534230723</v>
       </c>
       <c r="C68" t="s">
         <v>32</v>
@@ -1388,7 +1388,7 @@
         <v>17</v>
       </c>
       <c r="B69">
-        <v>13.81219038420153</v>
+        <v>6.937813763268943</v>
       </c>
       <c r="C69" t="s">
         <v>32</v>
@@ -1399,7 +1399,7 @@
         <v>18</v>
       </c>
       <c r="B70">
-        <v>31.85785010194586</v>
+        <v>15.4782711480731</v>
       </c>
       <c r="C70" t="s">
         <v>32</v>
@@ -1410,7 +1410,7 @@
         <v>19</v>
       </c>
       <c r="B71">
-        <v>4.702669778896399</v>
+        <v>0.6524448268638271</v>
       </c>
       <c r="C71" t="s">
         <v>32</v>
@@ -1421,7 +1421,7 @@
         <v>20</v>
       </c>
       <c r="B72">
-        <v>25.55803571858191</v>
+        <v>2.055254347076264</v>
       </c>
       <c r="C72" t="s">
         <v>32</v>
@@ -1432,7 +1432,7 @@
         <v>21</v>
       </c>
       <c r="B73">
-        <v>6.172081461636783</v>
+        <v>2.005149077662273</v>
       </c>
       <c r="C73" t="s">
         <v>32</v>
@@ -1443,7 +1443,7 @@
         <v>22</v>
       </c>
       <c r="B74">
-        <v>69.57627624060105</v>
+        <v>36.86804480404135</v>
       </c>
       <c r="C74" t="s">
         <v>32</v>
@@ -1454,7 +1454,7 @@
         <v>23</v>
       </c>
       <c r="B75">
-        <v>2.347076112238387</v>
+        <v>0.4231598468599666</v>
       </c>
       <c r="C75" t="s">
         <v>32</v>
@@ -1465,7 +1465,7 @@
         <v>24</v>
       </c>
       <c r="B76">
-        <v>50.76367145760086</v>
+        <v>42.66549156340798</v>
       </c>
       <c r="C76" t="s">
         <v>32</v>
@@ -1476,7 +1476,7 @@
         <v>25</v>
       </c>
       <c r="B77">
-        <v>56.26842720480796</v>
+        <v>8.969068329768112</v>
       </c>
       <c r="C77" t="s">
         <v>32</v>
@@ -1487,7 +1487,7 @@
         <v>26</v>
       </c>
       <c r="B78">
-        <v>41.96251417765986</v>
+        <v>7.737114786834848</v>
       </c>
       <c r="C78" t="s">
         <v>32</v>
@@ -1498,7 +1498,7 @@
         <v>27</v>
       </c>
       <c r="B79">
-        <v>2.891222480621525</v>
+        <v>0.2984921335798238</v>
       </c>
       <c r="C79" t="s">
         <v>32</v>
@@ -1509,7 +1509,7 @@
         <v>28</v>
       </c>
       <c r="B80">
-        <v>5.164859774939202</v>
+        <v>1.40195898533738</v>
       </c>
       <c r="C80" t="s">
         <v>32</v>
@@ -1520,7 +1520,7 @@
         <v>29</v>
       </c>
       <c r="B81">
-        <v>26.22520367785448</v>
+        <v>5.175996558062884</v>
       </c>
       <c r="C81" t="s">
         <v>32</v>
@@ -1531,7 +1531,7 @@
         <v>30</v>
       </c>
       <c r="B82">
-        <v>136.8689306232771</v>
+        <v>23.84431714789717</v>
       </c>
       <c r="C82" t="s">
         <v>32</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>40</v>
       </c>
       <c r="C6">
-        <v>0.05454545454545454</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="D6">
-        <v>0.8762696636277618</v>
+        <v>0.7554968749288828</v>
       </c>
       <c r="E6">
         <v>12.29804292220766</v>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>0.2129119028115045</v>
       </c>
       <c r="E7">
-        <v>-25.1958354910948</v>
+        <v>-25.07256730607227</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -1787,19 +1787,19 @@
         <v>40</v>
       </c>
       <c r="C9">
-        <v>0.2363636363636364</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="D9">
-        <v>0.3502013891792957</v>
+        <v>0.2757578478275093</v>
       </c>
       <c r="E9">
-        <v>60.26697272766927</v>
+        <v>51.82729044141305</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -1938,13 +1938,13 @@
         <v>0.7554968749288828</v>
       </c>
       <c r="E14">
-        <v>28.8018048092385</v>
+        <v>29.18425068373712</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -1967,13 +1967,13 @@
         <v>0.2757578478275093</v>
       </c>
       <c r="E15">
-        <v>6.675769969497495</v>
+        <v>6.80644941501278</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>0.640428787412791</v>
       </c>
       <c r="E20">
-        <v>-50.72043139210189</v>
+        <v>-50.47503169807199</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
@@ -2170,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>-0.9676203685337575</v>
+        <v>-0.9667603126735602</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>-2.946864739012744</v>
+        <v>-2.571238002190559</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -2367,19 +2367,19 @@
         <v>40</v>
       </c>
       <c r="C29">
-        <v>0.1272727272727273</v>
+        <v>-0.1272727272727273</v>
       </c>
       <c r="D29">
         <v>0.640428787412791</v>
       </c>
       <c r="E29">
-        <v>1.88799552863405</v>
+        <v>-0.2735588329307728</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.8645788630072678</v>
+        <v>0.7859807845520617</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.640428787412791</v>
       </c>
       <c r="E30">
-        <v>1.929879640341924</v>
+        <v>1.973474081493142</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0.8645788630072678</v>
+        <v>0.7859807845520617</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -2425,19 +2425,19 @@
         <v>40</v>
       </c>
       <c r="C31">
-        <v>-0.3454545454545455</v>
+        <v>-0.2</v>
       </c>
       <c r="D31">
-        <v>0.1611249492890519</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="E31">
-        <v>-6.205119843407868</v>
+        <v>-2.558710576002405</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.4833748478671556</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -2454,19 +2454,19 @@
         <v>40</v>
       </c>
       <c r="C32">
-        <v>-0.05454545454545454</v>
+        <v>0.01818181818181818</v>
       </c>
       <c r="D32">
-        <v>0.8762696636277618</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>-0.237995351762246</v>
+        <v>0.01050994528115634</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0.9463712367179828</v>
+        <v>1</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -2483,19 +2483,19 @@
         <v>40</v>
       </c>
       <c r="C33">
-        <v>-0.01818181818181818</v>
+        <v>-0.09090909090909091</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0.7554968749288828</v>
       </c>
       <c r="E33">
-        <v>-1.128634712152777</v>
+        <v>-2.947744029334416</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0.8499339842949932</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -2509,22 +2509,22 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C34">
-        <v>-0.05454545454545454</v>
+        <v>-0.5636363636363636</v>
       </c>
       <c r="D34">
-        <v>0.8762696636277618</v>
+        <v>0.01951748118217767</v>
       </c>
       <c r="E34">
-        <v>-2.376434052457029</v>
+        <v>-2.228797948318025</v>
       </c>
       <c r="F34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>0.9463712367179828</v>
+        <v>0.1317429979796992</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -2541,19 +2541,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>0.1272727272727273</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="D35">
-        <v>0.640428787412791</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="E35">
-        <v>0.6751647044356626</v>
+        <v>1.109201995922639</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.8645788630072678</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -2576,13 +2576,13 @@
         <v>0.1524062839567493</v>
       </c>
       <c r="E36">
-        <v>17.99883157716391</v>
+        <v>6.7131117056469</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0.4833748478671556</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
@@ -2599,19 +2599,19 @@
         <v>41</v>
       </c>
       <c r="C37">
-        <v>0.5272727272727272</v>
+        <v>0.6</v>
       </c>
       <c r="D37">
-        <v>0.02927250918630464</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="E37">
-        <v>12.02840796326513</v>
+        <v>8.617580373632418</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
       </c>
       <c r="G37">
-        <v>0.2634525826767418</v>
+        <v>0.1317429979796992</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
@@ -2628,19 +2628,19 @@
         <v>40</v>
       </c>
       <c r="C38">
-        <v>-0.1272727272727273</v>
+        <v>-0.2727272727272727</v>
       </c>
       <c r="D38">
-        <v>0.640428787412791</v>
+        <v>0.2757578478275093</v>
       </c>
       <c r="E38">
-        <v>-5.064432508662249</v>
+        <v>-3.623710463999429</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.8645788630072678</v>
+        <v>0.5318187065244823</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
@@ -2657,19 +2657,19 @@
         <v>40</v>
       </c>
       <c r="C39">
-        <v>0.05454545454545454</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="D39">
-        <v>0.8762696636277618</v>
+        <v>0.7554968749288828</v>
       </c>
       <c r="E39">
-        <v>4.264841360995097</v>
+        <v>1.827756078009721</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>0.9463712367179828</v>
+        <v>0.8499339842949932</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
@@ -2686,22 +2686,22 @@
         <v>41</v>
       </c>
       <c r="C40">
-        <v>0.6727272727272727</v>
+        <v>0.7818181818181819</v>
       </c>
       <c r="D40">
-        <v>0.005069309556701596</v>
+        <v>0.001076632864587701</v>
       </c>
       <c r="E40">
-        <v>158.2381810484503</v>
+        <v>15.70346941651842</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
       </c>
       <c r="G40">
-        <v>0.1368713580309431</v>
+        <v>0.02906908734386793</v>
       </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="s">
         <v>31</v>
@@ -2721,13 +2721,13 @@
         <v>0.01951748118217767</v>
       </c>
       <c r="E41">
-        <v>13.4912660482552</v>
+        <v>10.17643495220999</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
       </c>
       <c r="G41">
-        <v>0.2634525826767418</v>
+        <v>0.1317429979796992</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
@@ -2744,19 +2744,19 @@
         <v>40</v>
       </c>
       <c r="C42">
-        <v>-0.2727272727272727</v>
+        <v>-0.4181818181818182</v>
       </c>
       <c r="D42">
-        <v>0.2757578478275093</v>
+        <v>0.0867681727038756</v>
       </c>
       <c r="E42">
-        <v>-6.290549945004511</v>
+        <v>-5.223625993828157</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>0.620455157611896</v>
+        <v>0.3904567771674402</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
@@ -2773,19 +2773,19 @@
         <v>40</v>
       </c>
       <c r="C43">
-        <v>0.2</v>
+        <v>-0.4181818181818182</v>
       </c>
       <c r="D43">
-        <v>0.4362749288405292</v>
+        <v>0.0867681727038756</v>
       </c>
       <c r="E43">
-        <v>1.312797127663078</v>
+        <v>-4.654990769883248</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.8413873627638778</v>
+        <v>0.3904567771674402</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
@@ -2802,19 +2802,19 @@
         <v>40</v>
       </c>
       <c r="C44">
-        <v>0.1272727272727273</v>
+        <v>0.3090909090909091</v>
       </c>
       <c r="D44">
-        <v>0.640428787412791</v>
+        <v>0.2129119028115045</v>
       </c>
       <c r="E44">
-        <v>1.230822536333226</v>
+        <v>0.3259454295923828</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
       </c>
       <c r="G44">
-        <v>0.8645788630072678</v>
+        <v>0.4422016443008171</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
@@ -2831,19 +2831,19 @@
         <v>40</v>
       </c>
       <c r="C45">
-        <v>0.01818181818181818</v>
+        <v>-0.05454545454545454</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0.8762696636277618</v>
       </c>
       <c r="E45">
-        <v>0.3219345441494182</v>
+        <v>-0.221433219376887</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>0.9463712367179828</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
@@ -2860,19 +2860,19 @@
         <v>40</v>
       </c>
       <c r="C46">
-        <v>-0.1636363636363636</v>
+        <v>-0.2</v>
       </c>
       <c r="D46">
-        <v>0.5334165134726945</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="E46">
-        <v>-4.962274999737982</v>
+        <v>-3.666382029996921</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>0.8645788630072678</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
@@ -2889,19 +2889,19 @@
         <v>40</v>
       </c>
       <c r="C47">
-        <v>-0.2727272727272727</v>
+        <v>-0.2363636363636364</v>
       </c>
       <c r="D47">
-        <v>0.2757578478275093</v>
+        <v>0.3502013891792957</v>
       </c>
       <c r="E47">
-        <v>-20.97829234924756</v>
+        <v>-19.00409982565504</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>0.620455157611896</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
@@ -2918,19 +2918,19 @@
         <v>40</v>
       </c>
       <c r="C48">
-        <v>0.3454545454545455</v>
+        <v>0.3818181818181818</v>
       </c>
       <c r="D48">
-        <v>0.1611249492890519</v>
+        <v>0.1194709867717008</v>
       </c>
       <c r="E48">
-        <v>0.5017752893508248</v>
+        <v>0.2366864085983684</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0.4833748478671556</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="H48" t="b">
         <v>0</v>
@@ -2947,19 +2947,19 @@
         <v>40</v>
       </c>
       <c r="C49">
-        <v>-0.2</v>
+        <v>-0.3090909090909091</v>
       </c>
       <c r="D49">
-        <v>0.4362749288405292</v>
+        <v>0.2129119028115045</v>
       </c>
       <c r="E49">
-        <v>-4.848973085877031</v>
+        <v>-4.816873394037015</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0.8413873627638778</v>
+        <v>0.4422016443008171</v>
       </c>
       <c r="H49" t="b">
         <v>0</v>
@@ -2976,19 +2976,19 @@
         <v>40</v>
       </c>
       <c r="C50">
-        <v>0.3454545454545455</v>
+        <v>0.2</v>
       </c>
       <c r="D50">
-        <v>0.1611249492890519</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="E50">
-        <v>11.04515380771469</v>
+        <v>1.293033500920147</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0.4833748478671556</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
@@ -3005,19 +3005,19 @@
         <v>40</v>
       </c>
       <c r="C51">
-        <v>-0.3090909090909091</v>
+        <v>-0.2</v>
       </c>
       <c r="D51">
-        <v>0.2129119028115045</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="E51">
-        <v>-5.207962723243465</v>
+        <v>-0.1781542748160071</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0.5748621375910622</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
@@ -3034,19 +3034,19 @@
         <v>40</v>
       </c>
       <c r="C52">
-        <v>0.3818181818181818</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="D52">
-        <v>0.1194709867717008</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="E52">
-        <v>0.9576327922959754</v>
+        <v>0.1675317483546054</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
       </c>
       <c r="G52">
-        <v>0.4833748478671556</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
@@ -3063,19 +3063,19 @@
         <v>40</v>
       </c>
       <c r="C53">
-        <v>0.3818181818181818</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="D53">
-        <v>0.1194709867717008</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="E53">
-        <v>2.363778198315053</v>
+        <v>0.7495155064633311</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
       </c>
       <c r="G53">
-        <v>0.4833748478671556</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="H53" t="b">
         <v>0</v>
@@ -3092,19 +3092,19 @@
         <v>40</v>
       </c>
       <c r="C54">
-        <v>-0.05454545454545454</v>
+        <v>-0.2</v>
       </c>
       <c r="D54">
-        <v>0.8762696636277618</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="E54">
-        <v>-5.120842894912045</v>
+        <v>-10.89915101949616</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>0.9463712367179828</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="H54" t="b">
         <v>0</v>
@@ -3121,19 +3121,19 @@
         <v>40</v>
       </c>
       <c r="C55">
-        <v>-0.05454545454545454</v>
+        <v>-0.01818181818181818</v>
       </c>
       <c r="D55">
-        <v>0.8762696636277618</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>-1.251441975056784</v>
+        <v>-0.9987992136124246</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0.9463712367179828</v>
+        <v>1</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
@@ -3150,19 +3150,19 @@
         <v>40</v>
       </c>
       <c r="C56">
-        <v>0.1636363636363636</v>
+        <v>-0.05454545454545454</v>
       </c>
       <c r="D56">
-        <v>0.5334165134726945</v>
+        <v>0.8762696636277618</v>
       </c>
       <c r="E56">
-        <v>5.201483689539216</v>
+        <v>-0.2193499075591784</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
       </c>
       <c r="G56">
-        <v>0.6858212316077501</v>
+        <v>0.9099723429980604</v>
       </c>
       <c r="H56" t="b">
         <v>0</v>
@@ -3179,22 +3179,22 @@
         <v>42</v>
       </c>
       <c r="C57">
-        <v>-0.5272727272727272</v>
+        <v>-0.6</v>
       </c>
       <c r="D57">
-        <v>0.02927250918630464</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="E57">
-        <v>-1.223698183262965</v>
+        <v>-0.8812606367287721</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
       </c>
       <c r="G57">
-        <v>0.1317262913383709</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="H57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="s">
         <v>32</v>
@@ -3208,19 +3208,19 @@
         <v>40</v>
       </c>
       <c r="C58">
-        <v>0.05454545454545454</v>
+        <v>0.01818181818181818</v>
       </c>
       <c r="D58">
-        <v>0.8762696636277618</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>0.1073480995923699</v>
+        <v>0.01052558895807554</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
       </c>
       <c r="G58">
-        <v>0.9099723429980604</v>
+        <v>1</v>
       </c>
       <c r="H58" t="b">
         <v>0</v>
@@ -3234,25 +3234,25 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C59">
-        <v>-0.4545454545454545</v>
+        <v>-0.6</v>
       </c>
       <c r="D59">
-        <v>0.06170669002831275</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="E59">
-        <v>-1.49480678961878</v>
+        <v>-1.166090323755766</v>
       </c>
       <c r="F59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>0.2380115186806349</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="H59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="s">
         <v>32</v>
@@ -3263,22 +3263,22 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C60">
-        <v>-0.3090909090909091</v>
+        <v>-0.4909090909090909</v>
       </c>
       <c r="D60">
-        <v>0.2129119028115045</v>
+        <v>0.04296014602842502</v>
       </c>
       <c r="E60">
-        <v>-1.724191049650246</v>
+        <v>-1.797893960349319</v>
       </c>
       <c r="F60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>0.3832414250607081</v>
+        <v>0.0892249186744212</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
@@ -3295,19 +3295,19 @@
         <v>40</v>
       </c>
       <c r="C61">
-        <v>0.05454545454545454</v>
+        <v>-0.3454545454545455</v>
       </c>
       <c r="D61">
-        <v>0.8762696636277618</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="E61">
-        <v>0.7046674133388144</v>
+        <v>-0.3463926746117606</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>0.9099723429980604</v>
+        <v>0.2416874239335778</v>
       </c>
       <c r="H61" t="b">
         <v>0</v>
@@ -3324,22 +3324,22 @@
         <v>42</v>
       </c>
       <c r="C62">
-        <v>-0.6363636363636364</v>
+        <v>-0.7818181818181819</v>
       </c>
       <c r="D62">
-        <v>0.008123423304273514</v>
+        <v>0.001076632864587701</v>
       </c>
       <c r="E62">
-        <v>-1.131010454359694</v>
+        <v>-0.318203772046579</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
       </c>
       <c r="G62">
-        <v>0.1096662146076924</v>
+        <v>0.01453454367193396</v>
       </c>
       <c r="H62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="s">
         <v>32</v>
@@ -3350,25 +3350,25 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C63">
-        <v>-0.02222222222222222</v>
+        <v>-0.6</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0.02004466862262744</v>
       </c>
       <c r="E63">
-        <v>-0.7107909252082804</v>
+        <v>-1.912873237103457</v>
       </c>
       <c r="F63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>0.04510050440091173</v>
       </c>
       <c r="H63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="s">
         <v>32</v>
@@ -3379,25 +3379,25 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C64">
-        <v>-0.3090909090909091</v>
+        <v>-0.6727272727272727</v>
       </c>
       <c r="D64">
-        <v>0.2129119028115045</v>
+        <v>0.005069309556701596</v>
       </c>
       <c r="E64">
-        <v>-3.715745054080492</v>
+        <v>-1.810720555627992</v>
       </c>
       <c r="F64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>0.3832414250607081</v>
+        <v>0.02737427160618862</v>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="s">
         <v>32</v>
@@ -3411,19 +3411,19 @@
         <v>40</v>
       </c>
       <c r="C65">
-        <v>0.1636363636363636</v>
+        <v>-0.2</v>
       </c>
       <c r="D65">
-        <v>0.5334165134726945</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="E65">
-        <v>1.929532137585396</v>
+        <v>-0.3699955048688119</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
       </c>
       <c r="G65">
-        <v>0.6858212316077501</v>
+        <v>0.5354283217588313</v>
       </c>
       <c r="H65" t="b">
         <v>0</v>
@@ -3440,19 +3440,19 @@
         <v>40</v>
       </c>
       <c r="C66">
-        <v>-0.2</v>
+        <v>-0.3090909090909091</v>
       </c>
       <c r="D66">
-        <v>0.4362749288405292</v>
+        <v>0.2129119028115045</v>
       </c>
       <c r="E66">
-        <v>-1.365576859815874</v>
+        <v>-1.194211812546458</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
       </c>
       <c r="G66">
-        <v>0.619969635720752</v>
+        <v>0.3025590197847696</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>40</v>
       </c>
       <c r="C67">
-        <v>0.3090909090909091</v>
+        <v>-0.2</v>
       </c>
       <c r="D67">
-        <v>0.2129119028115045</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="E67">
-        <v>5.771986424590998</v>
+        <v>-0.1992511491900825</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>0.3832414250607081</v>
+        <v>0.5354283217588313</v>
       </c>
       <c r="H67" t="b">
         <v>0</v>
@@ -3498,22 +3498,22 @@
         <v>42</v>
       </c>
       <c r="C68">
-        <v>-0.5636363636363636</v>
+        <v>-0.6363636363636364</v>
       </c>
       <c r="D68">
-        <v>0.01951748118217767</v>
+        <v>0.008123423304273514</v>
       </c>
       <c r="E68">
-        <v>-0.8242533106763592</v>
+        <v>-0.3699213159603518</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
       </c>
       <c r="G68">
-        <v>0.1317262913383709</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="H68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="s">
         <v>32</v>
@@ -3524,25 +3524,25 @@
         <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C69">
-        <v>-0.2727272727272727</v>
+        <v>-0.6</v>
       </c>
       <c r="D69">
-        <v>0.2757578478275093</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="E69">
-        <v>-0.8700077196283497</v>
+        <v>-0.4219131176919373</v>
       </c>
       <c r="F69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>0.4379683465495736</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="H69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="s">
         <v>32</v>
@@ -3553,25 +3553,25 @@
         <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C70">
-        <v>-0.3454545454545455</v>
+        <v>-0.5636363636363636</v>
       </c>
       <c r="D70">
-        <v>0.1611249492890519</v>
+        <v>0.01951748118217767</v>
       </c>
       <c r="E70">
-        <v>-2.052022542788601</v>
+        <v>-1.616720649837422</v>
       </c>
       <c r="F70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>0.3625311359003667</v>
+        <v>0.04510050440091173</v>
       </c>
       <c r="H70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="s">
         <v>32</v>
@@ -3585,22 +3585,22 @@
         <v>42</v>
       </c>
       <c r="C71">
-        <v>-0.5272727272727272</v>
+        <v>-0.6727272727272727</v>
       </c>
       <c r="D71">
-        <v>0.02927250918630464</v>
+        <v>0.005069309556701596</v>
       </c>
       <c r="E71">
-        <v>-0.3187158780675844</v>
+        <v>-0.0422227519853562</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>0.1317262913383709</v>
+        <v>0.02737427160618862</v>
       </c>
       <c r="H71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="s">
         <v>32</v>
@@ -3614,19 +3614,19 @@
         <v>40</v>
       </c>
       <c r="C72">
-        <v>0.2</v>
+        <v>-0.1636363636363636</v>
       </c>
       <c r="D72">
-        <v>0.4362749288405292</v>
+        <v>0.5334165134726945</v>
       </c>
       <c r="E72">
-        <v>1.527475463215183</v>
+        <v>-0.1319235636535279</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
       </c>
       <c r="G72">
-        <v>0.619969635720752</v>
+        <v>0.5760898345505101</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
@@ -3643,22 +3643,22 @@
         <v>42</v>
       </c>
       <c r="C73">
-        <v>-0.6363636363636364</v>
+        <v>-0.6</v>
       </c>
       <c r="D73">
-        <v>0.008123423304273514</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="E73">
-        <v>-0.6747996311100496</v>
+        <v>-0.2829370814975902</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
       </c>
       <c r="G73">
-        <v>0.1096662146076924</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="H73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="s">
         <v>32</v>
@@ -3672,19 +3672,19 @@
         <v>40</v>
       </c>
       <c r="C74">
-        <v>0.09090909090909091</v>
+        <v>-0.1636363636363636</v>
       </c>
       <c r="D74">
-        <v>0.7554968749288828</v>
+        <v>0.5334165134726945</v>
       </c>
       <c r="E74">
-        <v>1.078953589110945</v>
+        <v>-0.8500269406817593</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
       </c>
       <c r="G74">
-        <v>0.8499339842949932</v>
+        <v>0.5760898345505101</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
@@ -3701,19 +3701,19 @@
         <v>40</v>
       </c>
       <c r="C75">
-        <v>-0.3818181818181818</v>
+        <v>-0.3454545454545455</v>
       </c>
       <c r="D75">
-        <v>0.1194709867717008</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="E75">
-        <v>-0.1883944983551364</v>
+        <v>-0.04021433875215356</v>
       </c>
       <c r="F75" t="b">
         <v>0</v>
       </c>
       <c r="G75">
-        <v>0.3225716642835921</v>
+        <v>0.2416874239335778</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
@@ -3730,22 +3730,22 @@
         <v>42</v>
       </c>
       <c r="C76">
-        <v>-0.5636363636363636</v>
+        <v>-0.9454545454545454</v>
       </c>
       <c r="D76">
-        <v>0.01951748118217767</v>
+        <v>5.939321753611893E-05</v>
       </c>
       <c r="E76">
-        <v>-2.496310605478456</v>
+        <v>-1.926855737509735</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
       </c>
       <c r="G76">
-        <v>0.1317262913383709</v>
+        <v>0.001603616873475211</v>
       </c>
       <c r="H76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="s">
         <v>32</v>
@@ -3759,19 +3759,19 @@
         <v>40</v>
       </c>
       <c r="C77">
-        <v>0.2727272727272727</v>
+        <v>-0.3454545454545455</v>
       </c>
       <c r="D77">
-        <v>0.2757578478275093</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="E77">
-        <v>2.690581337962379</v>
+        <v>-0.5839479430430228</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
       </c>
       <c r="G77">
-        <v>0.4379683465495736</v>
+        <v>0.2416874239335778</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
@@ -3788,19 +3788,19 @@
         <v>40</v>
       </c>
       <c r="C78">
-        <v>-0.3454545454545455</v>
+        <v>-0.3818181818181818</v>
       </c>
       <c r="D78">
-        <v>0.1611249492890519</v>
+        <v>0.1194709867717008</v>
       </c>
       <c r="E78">
-        <v>-3.037658223343728</v>
+        <v>-0.893811789220924</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
       </c>
       <c r="G78">
-        <v>0.3625311359003667</v>
+        <v>0.2150477761890614</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
@@ -3817,19 +3817,19 @@
         <v>40</v>
       </c>
       <c r="C79">
-        <v>-0.09090909090909091</v>
+        <v>-0.2727272727272727</v>
       </c>
       <c r="D79">
-        <v>0.7554968749288828</v>
+        <v>0.2757578478275093</v>
       </c>
       <c r="E79">
-        <v>-0.07083273711645129</v>
+        <v>-0.03979407691186252</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
       </c>
       <c r="G79">
-        <v>0.8499339842949932</v>
+        <v>0.3722730945671376</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
@@ -3843,25 +3843,25 @@
         <v>28</v>
       </c>
       <c r="B80" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C80">
-        <v>-0.3818181818181818</v>
+        <v>-0.7090909090909091</v>
       </c>
       <c r="D80">
-        <v>0.1194709867717008</v>
+        <v>0.003093449322761233</v>
       </c>
       <c r="E80">
-        <v>-0.2642831506577579</v>
+        <v>-0.1131228514685746</v>
       </c>
       <c r="F80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>0.3225716642835921</v>
+        <v>0.02737427160618862</v>
       </c>
       <c r="H80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="s">
         <v>32</v>
@@ -3875,19 +3875,19 @@
         <v>40</v>
       </c>
       <c r="C81">
-        <v>0.09090909090909091</v>
+        <v>-0.1636363636363636</v>
       </c>
       <c r="D81">
-        <v>0.7554968749288828</v>
+        <v>0.5334165134726945</v>
       </c>
       <c r="E81">
-        <v>0.518834885629095</v>
+        <v>-0.2106418610824311</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
       </c>
       <c r="G81">
-        <v>0.8499339842949932</v>
+        <v>0.5760898345505101</v>
       </c>
       <c r="H81" t="b">
         <v>0</v>
@@ -3904,19 +3904,19 @@
         <v>40</v>
       </c>
       <c r="C82">
-        <v>-0.4181818181818182</v>
+        <v>-0.4545454545454545</v>
       </c>
       <c r="D82">
-        <v>0.0867681727038756</v>
+        <v>0.06170669002831275</v>
       </c>
       <c r="E82">
-        <v>-16.01094594835849</v>
+        <v>-2.778856561134424</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
       </c>
       <c r="G82">
-        <v>0.2928425828755802</v>
+        <v>0.1190057593403174</v>
       </c>
       <c r="H82" t="b">
         <v>0</v>
@@ -3984,13 +3984,13 @@
         <v>51</v>
       </c>
       <c r="D2">
-        <v>761.6208923809667</v>
+        <v>760.7249254466265</v>
       </c>
       <c r="E2" t="s">
         <v>52</v>
       </c>
       <c r="F2">
-        <v>-0.2260909356558147</v>
+        <v>-0.2261746967570854</v>
       </c>
       <c r="G2">
         <v>0.032</v>
@@ -4022,13 +4022,13 @@
         <v>55</v>
       </c>
       <c r="D3">
-        <v>366.3319961252419</v>
+        <v>367.2606063018525</v>
       </c>
       <c r="E3" t="s">
         <v>53</v>
       </c>
       <c r="F3">
-        <v>0.2668994540556223</v>
+        <v>0.2648479920039154</v>
       </c>
       <c r="G3">
         <v>0.064</v>
@@ -4060,13 +4060,13 @@
         <v>56</v>
       </c>
       <c r="D4">
-        <v>224.7380761411263</v>
+        <v>224.353388997563</v>
       </c>
       <c r="E4" t="s">
         <v>57</v>
       </c>
       <c r="F4">
-        <v>0.5541676416255105</v>
+        <v>0.5547028921705432</v>
       </c>
       <c r="G4">
         <v>0.016</v>
@@ -4098,22 +4098,22 @@
         <v>58</v>
       </c>
       <c r="D5">
-        <v>129.4391267822657</v>
+        <v>129.5997411597099</v>
       </c>
       <c r="E5" t="s">
         <v>53</v>
       </c>
       <c r="F5">
-        <v>0.4248216801896629</v>
+        <v>0.4240269355546554</v>
       </c>
       <c r="G5">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
       <c r="I5">
-        <v>0.1485</v>
+        <v>0.14985</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -4136,22 +4136,22 @@
         <v>59</v>
       </c>
       <c r="D6">
-        <v>396.9867302289278</v>
+        <v>397.3376949619366</v>
       </c>
       <c r="E6" t="s">
         <v>53</v>
       </c>
       <c r="F6">
-        <v>0.06755318270830513</v>
+        <v>0.06634262576201763</v>
       </c>
       <c r="G6">
-        <v>0.368</v>
+        <v>0.372</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
       <c r="I6">
-        <v>0.368</v>
+        <v>0.372</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -4174,13 +4174,13 @@
         <v>60</v>
       </c>
       <c r="D7">
-        <v>268.3271256090866</v>
+        <v>268.3843488563369</v>
       </c>
       <c r="E7" t="s">
         <v>53</v>
       </c>
       <c r="F7">
-        <v>0.2963717022814814</v>
+        <v>0.2948932915915125</v>
       </c>
       <c r="G7">
         <v>0.128</v>
@@ -4189,7 +4189,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>0.154125</v>
+        <v>0.151875</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>62</v>
       </c>
       <c r="D8">
-        <v>1693.713085159807</v>
+        <v>1693.572377630412</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
       </c>
       <c r="F8">
-        <v>1.952317116711837</v>
+        <v>1.963492695347469</v>
       </c>
       <c r="G8">
         <v>0.008</v>
@@ -4250,13 +4250,13 @@
         <v>65</v>
       </c>
       <c r="D9">
-        <v>1129.496421154182</v>
+        <v>1105.442682633964</v>
       </c>
       <c r="E9" t="s">
         <v>63</v>
       </c>
       <c r="F9">
-        <v>0.799935106403831</v>
+        <v>0.7693993695195105</v>
       </c>
       <c r="G9">
         <v>0.037</v>
@@ -4288,13 +4288,13 @@
         <v>66</v>
       </c>
       <c r="D10">
-        <v>1782.370173642894</v>
+        <v>1783.747283001748</v>
       </c>
       <c r="E10" t="s">
         <v>63</v>
       </c>
       <c r="F10">
-        <v>2.534872082659928</v>
+        <v>2.550187922032921</v>
       </c>
       <c r="G10">
         <v>0.002</v>
@@ -4326,13 +4326,13 @@
         <v>67</v>
       </c>
       <c r="D11">
-        <v>115.6159125568454</v>
+        <v>115.9169175023088</v>
       </c>
       <c r="E11" t="s">
         <v>57</v>
       </c>
       <c r="F11">
-        <v>0.5810480684921359</v>
+        <v>0.5806907208412467</v>
       </c>
       <c r="G11">
         <v>0.046</v>
@@ -4364,22 +4364,22 @@
         <v>68</v>
       </c>
       <c r="D12">
-        <v>657.6704961572924</v>
+        <v>657.7101841964064</v>
       </c>
       <c r="E12" t="s">
         <v>63</v>
       </c>
       <c r="F12">
-        <v>0.1013701825335883</v>
+        <v>0.1034156834909194</v>
       </c>
       <c r="G12">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>0.08437500000000001</v>
+        <v>0.081</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -4402,13 +4402,13 @@
         <v>69</v>
       </c>
       <c r="D13">
-        <v>935.8299155109588</v>
+        <v>935.9543755315033</v>
       </c>
       <c r="E13" t="s">
         <v>63</v>
       </c>
       <c r="F13">
-        <v>0.6347331955160713</v>
+        <v>0.6404001921754566</v>
       </c>
       <c r="G13">
         <v>0.013</v>
@@ -4440,13 +4440,13 @@
         <v>70</v>
       </c>
       <c r="D14">
-        <v>1538.67095069796</v>
+        <v>1538.9896816228</v>
       </c>
       <c r="E14" t="s">
         <v>63</v>
       </c>
       <c r="F14">
-        <v>2.149104894753795</v>
+        <v>2.14526620310061</v>
       </c>
       <c r="G14">
         <v>0.003</v>
@@ -4478,22 +4478,22 @@
         <v>71</v>
       </c>
       <c r="D15">
-        <v>105.8284781199683</v>
+        <v>106.0508645065856</v>
       </c>
       <c r="E15" t="s">
         <v>53</v>
       </c>
       <c r="F15">
-        <v>0.5473009298338968</v>
+        <v>0.5475345427642875</v>
       </c>
       <c r="G15">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
       <c r="H15">
         <v>3</v>
       </c>
       <c r="I15">
-        <v>0.099</v>
+        <v>0.0954</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -4516,13 +4516,13 @@
         <v>72</v>
       </c>
       <c r="D16">
-        <v>357.9410575011049</v>
+        <v>358.2471900781778</v>
       </c>
       <c r="E16" t="s">
         <v>53</v>
       </c>
       <c r="F16">
-        <v>0.2748280979863828</v>
+        <v>0.2733650304778945</v>
       </c>
       <c r="G16">
         <v>0.067</v>
@@ -4554,16 +4554,16 @@
         <v>74</v>
       </c>
       <c r="D17">
-        <v>1212.045814592163</v>
+        <v>1212.290285512076</v>
       </c>
       <c r="E17" t="s">
         <v>63</v>
       </c>
       <c r="F17">
-        <v>0.8788973203987732</v>
+        <v>0.8862346754334759</v>
       </c>
       <c r="G17">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -4592,13 +4592,13 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>264.4868870666639</v>
+        <v>264.7755914388144</v>
       </c>
       <c r="E18" t="s">
         <v>53</v>
       </c>
       <c r="F18">
-        <v>0.3555436460851074</v>
+        <v>0.3540237236356192</v>
       </c>
       <c r="G18">
         <v>0.07199999999999999</v>
@@ -4630,13 +4630,13 @@
         <v>76</v>
       </c>
       <c r="D19">
-        <v>315.147738113812</v>
+        <v>315.742931686186</v>
       </c>
       <c r="E19" t="s">
         <v>53</v>
       </c>
       <c r="F19">
-        <v>0.3212023867986695</v>
+        <v>0.3201513184889658</v>
       </c>
       <c r="G19">
         <v>0.077</v>
@@ -4668,13 +4668,13 @@
         <v>77</v>
       </c>
       <c r="D20">
-        <v>581.861334118146</v>
+        <v>582.0425431565758</v>
       </c>
       <c r="E20" t="s">
         <v>57</v>
       </c>
       <c r="F20">
-        <v>0.02475956723388233</v>
+        <v>0.02343161019889128</v>
       </c>
       <c r="G20">
         <v>0.045</v>
@@ -4706,22 +4706,22 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>361.3806737189068</v>
+        <v>360.9791588770014</v>
       </c>
       <c r="E21" t="s">
         <v>53</v>
       </c>
       <c r="F21">
-        <v>-0.2224204265910896</v>
+        <v>-0.2237239414552342</v>
       </c>
       <c r="G21">
-        <v>0.137</v>
+        <v>0.135</v>
       </c>
       <c r="H21">
         <v>2</v>
       </c>
       <c r="I21">
-        <v>0.154125</v>
+        <v>0.151875</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>79</v>
       </c>
       <c r="D22">
-        <v>293.8994321615687</v>
+        <v>293.9001375395331</v>
       </c>
       <c r="E22" t="s">
         <v>80</v>
       </c>
       <c r="F22">
-        <v>-0.8681548183541165</v>
+        <v>-0.8640682736791431</v>
       </c>
       <c r="G22">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H22">
         <v>2</v>
@@ -4782,22 +4782,22 @@
         <v>81</v>
       </c>
       <c r="D23">
-        <v>277.3645721203505</v>
+        <v>277.6387050865425</v>
       </c>
       <c r="E23" t="s">
         <v>53</v>
       </c>
       <c r="F23">
-        <v>0.1066059422236943</v>
+        <v>0.1056302916231145</v>
       </c>
       <c r="G23">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="H23">
         <v>3</v>
       </c>
       <c r="I23">
-        <v>0.3364615384615385</v>
+        <v>0.3375</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -4820,13 +4820,13 @@
         <v>82</v>
       </c>
       <c r="D24">
-        <v>70.97469521067249</v>
+        <v>70.82400226177489</v>
       </c>
       <c r="E24" t="s">
         <v>57</v>
       </c>
       <c r="F24">
-        <v>0.6357174844015216</v>
+        <v>0.635607010213476</v>
       </c>
       <c r="G24">
         <v>0.043</v>
@@ -4858,13 +4858,13 @@
         <v>83</v>
       </c>
       <c r="D25">
-        <v>749.4718399140905</v>
+        <v>749.675842484855</v>
       </c>
       <c r="E25" t="s">
         <v>53</v>
       </c>
       <c r="F25">
-        <v>0.09215851733241305</v>
+        <v>0.09363196262521593</v>
       </c>
       <c r="G25">
         <v>0.221</v>
@@ -4896,16 +4896,16 @@
         <v>84</v>
       </c>
       <c r="D26">
-        <v>977.7404030340294</v>
+        <v>977.9020420680006</v>
       </c>
       <c r="E26" t="s">
         <v>63</v>
       </c>
       <c r="F26">
-        <v>0.7733943148810701</v>
+        <v>0.7800106116165663</v>
       </c>
       <c r="G26">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -4934,22 +4934,22 @@
         <v>85</v>
       </c>
       <c r="D27">
-        <v>103.4086049849635</v>
+        <v>103.6178445452273</v>
       </c>
       <c r="E27" t="s">
         <v>53</v>
       </c>
       <c r="F27">
-        <v>0.4109449354793643</v>
+        <v>0.4090417947159767</v>
       </c>
       <c r="G27">
-        <v>0.132</v>
+        <v>0.134</v>
       </c>
       <c r="H27">
         <v>3</v>
       </c>
       <c r="I27">
-        <v>0.154125</v>
+        <v>0.151875</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -4972,22 +4972,22 @@
         <v>86</v>
       </c>
       <c r="D28">
-        <v>548.0485353772867</v>
+        <v>545.3414059931569</v>
       </c>
       <c r="E28" t="s">
         <v>53</v>
       </c>
       <c r="F28">
-        <v>-0.05464182481078903</v>
+        <v>-0.05707389280622494</v>
       </c>
       <c r="G28">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="H28">
         <v>2</v>
       </c>
       <c r="I28">
-        <v>0.154125</v>
+        <v>0.151875</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -5010,22 +5010,22 @@
         <v>51</v>
       </c>
       <c r="D29">
-        <v>67.25001813808062</v>
+        <v>18.1468302912281</v>
       </c>
       <c r="E29" t="s">
         <v>53</v>
       </c>
       <c r="F29">
-        <v>0.05117393303520407</v>
+        <v>0.06359447255811476</v>
       </c>
       <c r="G29">
-        <v>0.434</v>
+        <v>0.415</v>
       </c>
       <c r="H29">
         <v>3</v>
       </c>
       <c r="I29">
-        <v>0.48825</v>
+        <v>0.4871739130434783</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -5048,22 +5048,22 @@
         <v>55</v>
       </c>
       <c r="D30">
-        <v>135.6988243144004</v>
+        <v>113.6830247105905</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F30">
-        <v>-0.00466194112722167</v>
+        <v>0.5778600706925615</v>
       </c>
       <c r="G30">
-        <v>0.045</v>
+        <v>0.006</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0.2934</v>
+        <v>0.06075</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -5086,22 +5086,22 @@
         <v>56</v>
       </c>
       <c r="D31">
-        <v>52.32549498306765</v>
+        <v>14.88354558446479</v>
       </c>
       <c r="E31" t="s">
         <v>53</v>
       </c>
       <c r="F31">
-        <v>0.109288891996188</v>
+        <v>0.2737683817117395</v>
       </c>
       <c r="G31">
-        <v>0.398</v>
+        <v>0.247</v>
       </c>
       <c r="H31">
         <v>3</v>
       </c>
       <c r="I31">
-        <v>0.48825</v>
+        <v>0.3922941176470588</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -5124,22 +5124,22 @@
         <v>58</v>
       </c>
       <c r="D32">
-        <v>10.89184498677155</v>
+        <v>4.173783617492655</v>
       </c>
       <c r="E32" t="s">
         <v>53</v>
       </c>
       <c r="F32">
-        <v>-0.01238211305657333</v>
+        <v>0.03277716210422425</v>
       </c>
       <c r="G32">
-        <v>0.478</v>
+        <v>0.451</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>0.4963846153846154</v>
+        <v>0.49</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -5162,22 +5162,22 @@
         <v>59</v>
       </c>
       <c r="D33">
-        <v>153.3787802251116</v>
+        <v>123.0875237166268</v>
       </c>
       <c r="E33" t="s">
         <v>53</v>
       </c>
       <c r="F33">
-        <v>0.02694912321991344</v>
+        <v>0.3110665168284654</v>
       </c>
       <c r="G33">
-        <v>0.326</v>
+        <v>0.131</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>0.4630500000000001</v>
+        <v>0.29475</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -5200,22 +5200,22 @@
         <v>60</v>
       </c>
       <c r="D34">
-        <v>324.9365537246113</v>
+        <v>214.9518090430962</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F34">
-        <v>0.5181705609712171</v>
+        <v>1.456170759726224</v>
       </c>
       <c r="G34">
-        <v>0.184</v>
+        <v>0.025</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>0.2954117647058823</v>
+        <v>0.10125</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -5238,22 +5238,22 @@
         <v>62</v>
       </c>
       <c r="D35">
-        <v>27.21449156777539</v>
+        <v>12.59228926670447</v>
       </c>
       <c r="E35" t="s">
         <v>53</v>
       </c>
       <c r="F35">
-        <v>0.002922779149119443</v>
+        <v>-0.1009812995600061</v>
       </c>
       <c r="G35">
-        <v>0.498</v>
+        <v>0.405</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>0.498</v>
+        <v>0.4871739130434783</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -5276,22 +5276,22 @@
         <v>65</v>
       </c>
       <c r="D36">
-        <v>170.6191924335079</v>
+        <v>74.47665136494027</v>
       </c>
       <c r="E36" t="s">
         <v>53</v>
       </c>
       <c r="F36">
-        <v>-0.08792950247261251</v>
+        <v>-0.0003383871587138303</v>
       </c>
       <c r="G36">
-        <v>0.267</v>
+        <v>0.49</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>0.4005</v>
+        <v>0.49</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -5314,22 +5314,22 @@
         <v>66</v>
       </c>
       <c r="D37">
-        <v>62.71252183793935</v>
+        <v>47.19195464795877</v>
       </c>
       <c r="E37" t="s">
         <v>53</v>
       </c>
       <c r="F37">
-        <v>-0.3374086680952642</v>
+        <v>0.0116012177115685</v>
       </c>
       <c r="G37">
-        <v>0.118</v>
+        <v>0.464</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37">
-        <v>0.2934</v>
+        <v>0.49</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -5352,22 +5352,22 @@
         <v>67</v>
       </c>
       <c r="D38">
-        <v>51.40529400277442</v>
+        <v>36.89137490555263</v>
       </c>
       <c r="E38" t="s">
         <v>53</v>
       </c>
       <c r="F38">
-        <v>-0.2925986626695425</v>
+        <v>-0.2142709118259843</v>
       </c>
       <c r="G38">
-        <v>0.186</v>
+        <v>0.217</v>
       </c>
       <c r="H38">
         <v>2</v>
       </c>
       <c r="I38">
-        <v>0.2954117647058823</v>
+        <v>0.3906</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -5390,22 +5390,22 @@
         <v>68</v>
       </c>
       <c r="D39">
-        <v>294.4720208791497</v>
+        <v>227.7820589871915</v>
       </c>
       <c r="E39" t="s">
         <v>53</v>
       </c>
       <c r="F39">
-        <v>0.6290487308136677</v>
+        <v>-0.5848860013581277</v>
       </c>
       <c r="G39">
-        <v>0.113</v>
+        <v>0.351</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>0.2934</v>
+        <v>0.47385</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
@@ -5428,22 +5428,22 @@
         <v>69</v>
       </c>
       <c r="D40">
-        <v>498.3658184716266</v>
+        <v>114.3111642140532</v>
       </c>
       <c r="E40" t="s">
         <v>53</v>
       </c>
       <c r="F40">
-        <v>-1.430810241306536</v>
+        <v>-0.1494313654891954</v>
       </c>
       <c r="G40">
-        <v>0.143</v>
+        <v>0.282</v>
       </c>
       <c r="H40">
         <v>4</v>
       </c>
       <c r="I40">
-        <v>0.2934</v>
+        <v>0.4007368421052631</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
@@ -5466,22 +5466,22 @@
         <v>70</v>
       </c>
       <c r="D41">
-        <v>196.5821881713077</v>
+        <v>155.9401117997334</v>
       </c>
       <c r="E41" t="s">
         <v>53</v>
       </c>
       <c r="F41">
-        <v>-0.2590964002313141</v>
+        <v>-0.5449745701264236</v>
       </c>
       <c r="G41">
-        <v>0.121</v>
+        <v>0.156</v>
       </c>
       <c r="H41">
         <v>4</v>
       </c>
       <c r="I41">
-        <v>0.2934</v>
+        <v>0.324</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
@@ -5504,22 +5504,22 @@
         <v>71</v>
       </c>
       <c r="D42">
-        <v>57.78838556090096</v>
+        <v>28.80723400106806</v>
       </c>
       <c r="E42" t="s">
         <v>53</v>
       </c>
       <c r="F42">
-        <v>-0.1248841105759948</v>
+        <v>-0.08745717822599104</v>
       </c>
       <c r="G42">
-        <v>0.343</v>
+        <v>0.39</v>
       </c>
       <c r="H42">
         <v>2</v>
       </c>
       <c r="I42">
-        <v>0.4630500000000001</v>
+        <v>0.4871739130434783</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
@@ -5542,22 +5542,22 @@
         <v>72</v>
       </c>
       <c r="D43">
-        <v>177.5011666846259</v>
+        <v>131.1837535976336</v>
       </c>
       <c r="E43" t="s">
         <v>63</v>
       </c>
       <c r="F43">
-        <v>0.24726372428867</v>
+        <v>0.813999164062057</v>
       </c>
       <c r="G43">
-        <v>0.048</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>0.2934</v>
+        <v>0.06075</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -5580,22 +5580,22 @@
         <v>74</v>
       </c>
       <c r="D44">
-        <v>20.45328340547615</v>
+        <v>9.357281171826848</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F44">
-        <v>0.1320808761277379</v>
+        <v>0.6440625831583319</v>
       </c>
       <c r="G44">
-        <v>0.372</v>
+        <v>0.03</v>
       </c>
       <c r="H44">
         <v>3</v>
       </c>
       <c r="I44">
-        <v>0.4782857142857143</v>
+        <v>0.10125</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
@@ -5618,22 +5618,22 @@
         <v>75</v>
       </c>
       <c r="D45">
-        <v>194.4231476852588</v>
+        <v>99.65401283102314</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F45">
-        <v>0.3344575294347007</v>
+        <v>0.3687414854432933</v>
       </c>
       <c r="G45">
-        <v>0.06900000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45">
-        <v>0.2934</v>
+        <v>0.06075</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
@@ -5656,22 +5656,22 @@
         <v>76</v>
       </c>
       <c r="D46">
-        <v>94.90797018994768</v>
+        <v>75.87266356128049</v>
       </c>
       <c r="E46" t="s">
         <v>53</v>
       </c>
       <c r="F46">
-        <v>-0.1750032241223368</v>
+        <v>-0.01150416625838091</v>
       </c>
       <c r="G46">
-        <v>0.129</v>
+        <v>0.107</v>
       </c>
       <c r="H46">
         <v>2</v>
       </c>
       <c r="I46">
-        <v>0.2934</v>
+        <v>0.2626363636363636</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
@@ -5694,22 +5694,22 @@
         <v>77</v>
       </c>
       <c r="D47">
-        <v>264.1619171688866</v>
+        <v>202.5028770043829</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F47">
-        <v>0.603862997168899</v>
+        <v>1.492422920232245</v>
       </c>
       <c r="G47">
-        <v>0.081</v>
+        <v>0.02</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>0.2934</v>
+        <v>0.10125</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
@@ -5732,22 +5732,22 @@
         <v>78</v>
       </c>
       <c r="D48">
-        <v>5.639064915764338</v>
+        <v>1.690204324382488</v>
       </c>
       <c r="E48" t="s">
         <v>53</v>
       </c>
       <c r="F48">
-        <v>0.03609237835613271</v>
+        <v>0.5520628057188657</v>
       </c>
       <c r="G48">
-        <v>0.457</v>
+        <v>0.089</v>
       </c>
       <c r="H48">
         <v>3</v>
       </c>
       <c r="I48">
-        <v>0.4935600000000001</v>
+        <v>0.2403</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
@@ -5770,22 +5770,22 @@
         <v>79</v>
       </c>
       <c r="D49">
-        <v>105.898746505972</v>
+        <v>88.07331630847186</v>
       </c>
       <c r="E49" t="s">
         <v>53</v>
       </c>
       <c r="F49">
-        <v>0.1093406974093819</v>
+        <v>-0.05991526700373897</v>
       </c>
       <c r="G49">
-        <v>0.146</v>
+        <v>0.193</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I49">
-        <v>0.2934</v>
+        <v>0.3722142857142857</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
@@ -5808,22 +5808,22 @@
         <v>81</v>
       </c>
       <c r="D50">
-        <v>119.8505813666094</v>
+        <v>40.26942982855918</v>
       </c>
       <c r="E50" t="s">
         <v>53</v>
       </c>
       <c r="F50">
-        <v>-0.0607761884642651</v>
+        <v>-0.01073384003976919</v>
       </c>
       <c r="G50">
-        <v>0.163</v>
+        <v>0.49</v>
       </c>
       <c r="H50">
         <v>2</v>
       </c>
       <c r="I50">
-        <v>0.2934</v>
+        <v>0.49</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>82</v>
       </c>
       <c r="D51">
-        <v>149.2739937838233</v>
+        <v>61.76264161675046</v>
       </c>
       <c r="E51" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F51">
-        <v>-0.07162632356156561</v>
+        <v>0.1959673465479913</v>
       </c>
       <c r="G51">
-        <v>0.03</v>
+        <v>0.008</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I51">
-        <v>0.2934</v>
+        <v>0.06075</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
@@ -5884,22 +5884,22 @@
         <v>83</v>
       </c>
       <c r="D52">
-        <v>12.4864596753001</v>
+        <v>2.519589890469162</v>
       </c>
       <c r="E52" t="s">
         <v>53</v>
       </c>
       <c r="F52">
-        <v>0.04682910401910829</v>
+        <v>0.5487928193849572</v>
       </c>
       <c r="G52">
-        <v>0.425</v>
+        <v>0.075</v>
       </c>
       <c r="H52">
         <v>3</v>
       </c>
       <c r="I52">
-        <v>0.48825</v>
+        <v>0.225</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
@@ -5922,22 +5922,22 @@
         <v>84</v>
       </c>
       <c r="D53">
-        <v>26.25349444801241</v>
+        <v>9.69468052802868</v>
       </c>
       <c r="E53" t="s">
         <v>53</v>
       </c>
       <c r="F53">
-        <v>0.4653080227809582</v>
+        <v>0.25373363812818</v>
       </c>
       <c r="G53">
-        <v>0.083</v>
+        <v>0.247</v>
       </c>
       <c r="H53">
         <v>3</v>
       </c>
       <c r="I53">
-        <v>0.2934</v>
+        <v>0.3922941176470588</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
@@ -5960,22 +5960,22 @@
         <v>85</v>
       </c>
       <c r="D54">
-        <v>167.0590109613497</v>
+        <v>93.37583632616321</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F54">
-        <v>0.1109363185403507</v>
+        <v>0.2034756146320661</v>
       </c>
       <c r="G54">
-        <v>0.162</v>
+        <v>0.029</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54">
-        <v>0.2934</v>
+        <v>0.10125</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -5998,22 +5998,22 @@
         <v>86</v>
       </c>
       <c r="D55">
-        <v>241.2797722684294</v>
+        <v>85.64141124851885</v>
       </c>
       <c r="E55" t="s">
         <v>53</v>
       </c>
       <c r="F55">
-        <v>-0.4563381423369467</v>
+        <v>-0.03385175663194317</v>
       </c>
       <c r="G55">
-        <v>0.105</v>
+        <v>0.277</v>
       </c>
       <c r="H55">
         <v>4</v>
       </c>
       <c r="I55">
-        <v>0.2934</v>
+        <v>0.4007368421052631</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
@@ -6036,22 +6036,22 @@
         <v>51</v>
       </c>
       <c r="D56">
-        <v>72.13933769774226</v>
+        <v>10.65360682863999</v>
       </c>
       <c r="E56" t="s">
         <v>53</v>
       </c>
       <c r="F56">
-        <v>0.2989231234001183</v>
+        <v>-0.1054560211146521</v>
       </c>
       <c r="G56">
-        <v>0.237</v>
+        <v>0.163</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56">
-        <v>0.4334210526315789</v>
+        <v>0.4305</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
@@ -6074,22 +6074,22 @@
         <v>55</v>
       </c>
       <c r="D57">
-        <v>37.11232094043599</v>
+        <v>24.91581898666</v>
       </c>
       <c r="E57" t="s">
         <v>53</v>
       </c>
       <c r="F57">
-        <v>0.0004696558528783472</v>
+        <v>-0.04634532923890412</v>
       </c>
       <c r="G57">
-        <v>0.498</v>
+        <v>0.493</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>0.498</v>
+        <v>0.493</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -6112,22 +6112,22 @@
         <v>56</v>
       </c>
       <c r="D58">
-        <v>28.90000634733787</v>
+        <v>9.990325118339383</v>
       </c>
       <c r="E58" t="s">
         <v>53</v>
       </c>
       <c r="F58">
-        <v>-0.0530409851736976</v>
+        <v>0.08040421946637953</v>
       </c>
       <c r="G58">
-        <v>0.305</v>
+        <v>0.272</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58">
-        <v>0.4334210526315789</v>
+        <v>0.4305</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -6150,22 +6150,22 @@
         <v>58</v>
       </c>
       <c r="D59">
-        <v>19.81032332703572</v>
+        <v>13.52957110361621</v>
       </c>
       <c r="E59" t="s">
         <v>53</v>
       </c>
       <c r="F59">
-        <v>-0.3362454216821643</v>
+        <v>-0.02833171208801679</v>
       </c>
       <c r="G59">
-        <v>0.068</v>
+        <v>0.167</v>
       </c>
       <c r="H59">
         <v>2</v>
       </c>
       <c r="I59">
-        <v>0.324</v>
+        <v>0.4305</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
@@ -6188,22 +6188,22 @@
         <v>59</v>
       </c>
       <c r="D60">
-        <v>53.95343031697146</v>
+        <v>41.34335787242581</v>
       </c>
       <c r="E60" t="s">
         <v>53</v>
       </c>
       <c r="F60">
-        <v>-0.2585072294978915</v>
+        <v>-0.6188965902950945</v>
       </c>
       <c r="G60">
-        <v>0.116</v>
+        <v>0.222</v>
       </c>
       <c r="H60">
         <v>4</v>
       </c>
       <c r="I60">
-        <v>0.348</v>
+        <v>0.4305</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -6226,22 +6226,22 @@
         <v>60</v>
       </c>
       <c r="D61">
-        <v>26.80010861770792</v>
+        <v>7.645624680572847</v>
       </c>
       <c r="E61" t="s">
         <v>53</v>
       </c>
       <c r="F61">
-        <v>0.03598203695767895</v>
+        <v>-0.03920170043601672</v>
       </c>
       <c r="G61">
-        <v>0.418</v>
+        <v>0.387</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I61">
-        <v>0.4776923076923077</v>
+        <v>0.4660434782608696</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -6264,22 +6264,22 @@
         <v>62</v>
       </c>
       <c r="D62">
-        <v>15.91224391933893</v>
+        <v>2.618608506616466</v>
       </c>
       <c r="E62" t="s">
         <v>53</v>
       </c>
       <c r="F62">
-        <v>-0.232914578482432</v>
+        <v>-0.1795683154029569</v>
       </c>
       <c r="G62">
-        <v>0.207</v>
+        <v>0.262</v>
       </c>
       <c r="H62">
         <v>2</v>
       </c>
       <c r="I62">
-        <v>0.4334210526315789</v>
+        <v>0.4305</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -6302,22 +6302,22 @@
         <v>65</v>
       </c>
       <c r="D63">
-        <v>67.56294097297004</v>
+        <v>12.99472341907263</v>
       </c>
       <c r="E63" t="s">
         <v>53</v>
       </c>
       <c r="F63">
-        <v>-0.286560358090958</v>
+        <v>-0.02632935079596226</v>
       </c>
       <c r="G63">
-        <v>0.286</v>
+        <v>0.252</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I63">
-        <v>0.4334210526315789</v>
+        <v>0.4305</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -6340,22 +6340,22 @@
         <v>66</v>
       </c>
       <c r="D64">
-        <v>31.53903856718597</v>
+        <v>20.79026595101068</v>
       </c>
       <c r="E64" t="s">
         <v>53</v>
       </c>
       <c r="F64">
-        <v>-0.04222997491773842</v>
+        <v>-0.1276650931688715</v>
       </c>
       <c r="G64">
-        <v>0.275</v>
+        <v>0.242</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I64">
-        <v>0.4334210526315789</v>
+        <v>0.4305</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -6378,22 +6378,22 @@
         <v>67</v>
       </c>
       <c r="D65">
-        <v>19.45962174161331</v>
+        <v>9.261991768428196</v>
       </c>
       <c r="E65" t="s">
         <v>53</v>
       </c>
       <c r="F65">
-        <v>-0.07910549419763506</v>
+        <v>0.1212744105746165</v>
       </c>
       <c r="G65">
-        <v>0.345</v>
+        <v>0.19</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>0.4641428571428571</v>
+        <v>0.4305</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -6416,22 +6416,22 @@
         <v>68</v>
       </c>
       <c r="D66">
-        <v>98.44700785630522</v>
+        <v>72.69112413964704</v>
       </c>
       <c r="E66" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F66">
-        <v>1.27595217004255</v>
+        <v>-0.3296742436919484</v>
       </c>
       <c r="G66">
-        <v>0.047</v>
+        <v>0.451</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>0.324</v>
+        <v>0.4870800000000001</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -6454,22 +6454,22 @@
         <v>69</v>
       </c>
       <c r="D67">
-        <v>51.25499690888518</v>
+        <v>9.403169138378297</v>
       </c>
       <c r="E67" t="s">
         <v>53</v>
       </c>
       <c r="F67">
-        <v>-0.1227429090450409</v>
+        <v>-0.08460641918106622</v>
       </c>
       <c r="G67">
         <v>0.267</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I67">
-        <v>0.4334210526315789</v>
+        <v>0.4305</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -6492,22 +6492,22 @@
         <v>70</v>
       </c>
       <c r="D68">
-        <v>13.80639958278007</v>
+        <v>6.939301534230723</v>
       </c>
       <c r="E68" t="s">
         <v>53</v>
       </c>
       <c r="F68">
-        <v>0.07677927441331353</v>
+        <v>-0.03838151072776252</v>
       </c>
       <c r="G68">
-        <v>0.431</v>
+        <v>0.379</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68">
-        <v>0.4776923076923077</v>
+        <v>0.4660434782608696</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -6530,22 +6530,22 @@
         <v>71</v>
       </c>
       <c r="D69">
-        <v>13.81219038420153</v>
+        <v>6.937813763268943</v>
       </c>
       <c r="E69" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F69">
-        <v>-0.6537447000801866</v>
+        <v>-0.2779643891175675</v>
       </c>
       <c r="G69">
-        <v>0.035</v>
+        <v>0.103</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69">
-        <v>0.324</v>
+        <v>0.4305</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
@@ -6568,22 +6568,22 @@
         <v>72</v>
       </c>
       <c r="D70">
-        <v>31.85785010194586</v>
+        <v>15.4782711480731</v>
       </c>
       <c r="E70" t="s">
         <v>53</v>
       </c>
       <c r="F70">
-        <v>0.002148576398349902</v>
+        <v>0.001688032664516243</v>
       </c>
       <c r="G70">
-        <v>0.45</v>
+        <v>0.397</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I70">
-        <v>0.4776923076923077</v>
+        <v>0.4660434782608696</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
@@ -6606,22 +6606,22 @@
         <v>74</v>
       </c>
       <c r="D71">
-        <v>4.702669778896399</v>
+        <v>0.6524448268638271</v>
       </c>
       <c r="E71" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F71">
-        <v>0.6150341646973511</v>
+        <v>0.4151115811170266</v>
       </c>
       <c r="G71">
-        <v>0.028</v>
+        <v>0.057</v>
       </c>
       <c r="H71">
         <v>3</v>
       </c>
       <c r="I71">
-        <v>0.324</v>
+        <v>0.4305</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
@@ -6644,22 +6644,22 @@
         <v>75</v>
       </c>
       <c r="D72">
-        <v>25.55803571858191</v>
+        <v>2.055254347076264</v>
       </c>
       <c r="E72" t="s">
         <v>53</v>
       </c>
       <c r="F72">
-        <v>-0.01038641924530911</v>
+        <v>-0.1495657735096811</v>
       </c>
       <c r="G72">
-        <v>0.46</v>
+        <v>0.285</v>
       </c>
       <c r="H72">
         <v>2</v>
       </c>
       <c r="I72">
-        <v>0.4776923076923077</v>
+        <v>0.4305</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
@@ -6682,22 +6682,22 @@
         <v>76</v>
       </c>
       <c r="D73">
-        <v>6.172081461636783</v>
+        <v>2.005149077662273</v>
       </c>
       <c r="E73" t="s">
         <v>53</v>
       </c>
       <c r="F73">
-        <v>-0.4714523846393456</v>
+        <v>-0.09620043087540499</v>
       </c>
       <c r="G73">
-        <v>0.145</v>
+        <v>0.352</v>
       </c>
       <c r="H73">
         <v>2</v>
       </c>
       <c r="I73">
-        <v>0.3559090909090909</v>
+        <v>0.4660434782608696</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
@@ -6720,22 +6720,22 @@
         <v>77</v>
       </c>
       <c r="D74">
-        <v>69.57627624060105</v>
+        <v>36.86804480404135</v>
       </c>
       <c r="E74" t="s">
         <v>53</v>
       </c>
       <c r="F74">
-        <v>-0.2546322038739783</v>
+        <v>-0.2901112599301581</v>
       </c>
       <c r="G74">
-        <v>0.361</v>
+        <v>0.421</v>
       </c>
       <c r="H74">
         <v>4</v>
       </c>
       <c r="I74">
-        <v>0.4641428571428571</v>
+        <v>0.473625</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
@@ -6758,22 +6758,22 @@
         <v>78</v>
       </c>
       <c r="D75">
-        <v>2.347076112238387</v>
+        <v>0.4231598468599666</v>
       </c>
       <c r="E75" t="s">
         <v>53</v>
       </c>
       <c r="F75">
-        <v>0.5079327536875961</v>
+        <v>0.195836938122931</v>
       </c>
       <c r="G75">
-        <v>0.08400000000000001</v>
+        <v>0.287</v>
       </c>
       <c r="H75">
         <v>3</v>
       </c>
       <c r="I75">
-        <v>0.324</v>
+        <v>0.4305</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
@@ -6796,22 +6796,22 @@
         <v>79</v>
       </c>
       <c r="D76">
-        <v>50.76367145760086</v>
+        <v>42.66549156340798</v>
       </c>
       <c r="E76" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F76">
-        <v>-0.2131682879812256</v>
+        <v>-0.9793201021146232</v>
       </c>
       <c r="G76">
-        <v>0.116</v>
+        <v>0.04</v>
       </c>
       <c r="H76">
         <v>4</v>
       </c>
       <c r="I76">
-        <v>0.348</v>
+        <v>0.4305</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
@@ -6834,22 +6834,22 @@
         <v>81</v>
       </c>
       <c r="D77">
-        <v>56.26842720480796</v>
+        <v>8.969068329768112</v>
       </c>
       <c r="E77" t="s">
         <v>53</v>
       </c>
       <c r="F77">
-        <v>0.2568963422221175</v>
+        <v>-0.1629764420403951</v>
       </c>
       <c r="G77">
-        <v>0.135</v>
+        <v>0.157</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>0.3559090909090909</v>
+        <v>0.4305</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -6872,22 +6872,22 @@
         <v>82</v>
       </c>
       <c r="D78">
-        <v>41.96251417765986</v>
+        <v>7.737114786834848</v>
       </c>
       <c r="E78" t="s">
         <v>53</v>
       </c>
       <c r="F78">
-        <v>0.003373912407792653</v>
+        <v>0.1172858770498919</v>
       </c>
       <c r="G78">
-        <v>0.426</v>
+        <v>0.28</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>0.4776923076923077</v>
+        <v>0.4305</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
@@ -6910,22 +6910,22 @@
         <v>83</v>
       </c>
       <c r="D79">
-        <v>2.891222480621525</v>
+        <v>0.2984921335798238</v>
       </c>
       <c r="E79" t="s">
         <v>53</v>
       </c>
       <c r="F79">
-        <v>0.5038139996508454</v>
+        <v>0.1962593029019332</v>
       </c>
       <c r="G79">
-        <v>0.078</v>
+        <v>0.281</v>
       </c>
       <c r="H79">
         <v>3</v>
       </c>
       <c r="I79">
-        <v>0.324</v>
+        <v>0.4305</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
@@ -6948,22 +6948,22 @@
         <v>84</v>
       </c>
       <c r="D80">
-        <v>5.164859774939202</v>
+        <v>1.40195898533738</v>
       </c>
       <c r="E80" t="s">
         <v>53</v>
       </c>
       <c r="F80">
-        <v>0.5385832932638853</v>
+        <v>0.02120655059893682</v>
       </c>
       <c r="G80">
-        <v>0.061</v>
+        <v>0.492</v>
       </c>
       <c r="H80">
         <v>3</v>
       </c>
       <c r="I80">
-        <v>0.324</v>
+        <v>0.493</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
@@ -6986,22 +6986,22 @@
         <v>85</v>
       </c>
       <c r="D81">
-        <v>26.22520367785448</v>
+        <v>5.175996558062884</v>
       </c>
       <c r="E81" t="s">
         <v>53</v>
       </c>
       <c r="F81">
-        <v>-0.06916738475840215</v>
+        <v>-0.321389669373817</v>
       </c>
       <c r="G81">
-        <v>0.301</v>
+        <v>0.115</v>
       </c>
       <c r="H81">
         <v>2</v>
       </c>
       <c r="I81">
-        <v>0.4334210526315789</v>
+        <v>0.4305</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
@@ -7024,22 +7024,22 @@
         <v>86</v>
       </c>
       <c r="D82">
-        <v>136.8689306232771</v>
+        <v>23.84431714789717</v>
       </c>
       <c r="E82" t="s">
         <v>53</v>
       </c>
       <c r="F82">
-        <v>-1.195538481124017</v>
+        <v>0.0159868279422716</v>
       </c>
       <c r="G82">
-        <v>0.229</v>
+        <v>0.395</v>
       </c>
       <c r="H82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I82">
-        <v>0.4334210526315789</v>
+        <v>0.4660434782608696</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
@@ -7086,13 +7086,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.5158938248144128</v>
+        <v>0.5159726265648682</v>
       </c>
       <c r="C2">
         <v>-0.03846153846153846</v>
       </c>
       <c r="D2">
-        <v>5.610300263922954</v>
+        <v>5.614456653603256</v>
       </c>
       <c r="E2">
         <v>0.001</v>
@@ -7106,19 +7106,19 @@
         <v>31</v>
       </c>
       <c r="B3">
-        <v>0.004238851895810627</v>
+        <v>0.2308366236524081</v>
       </c>
       <c r="C3">
         <v>-0.03846153846153846</v>
       </c>
       <c r="D3">
-        <v>0.4591902116272888</v>
+        <v>2.689336689284548</v>
       </c>
       <c r="E3">
-        <v>0.285</v>
+        <v>0.017</v>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7126,16 +7126,16 @@
         <v>32</v>
       </c>
       <c r="B4">
-        <v>-0.006290288838290217</v>
+        <v>-0.1052665620255537</v>
       </c>
       <c r="C4">
         <v>-0.03846153846153846</v>
       </c>
       <c r="D4">
-        <v>0.3406099654413746</v>
+        <v>-0.7250507386720375</v>
       </c>
       <c r="E4">
-        <v>0.326</v>
+        <v>0.243</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
